--- a/activity/M01A06/M01A06_SeccionInicioEntrega.xlsx
+++ b/activity/M01A06/M01A06_SeccionInicioEntrega.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{229F7E1C-E500-4C3F-A11D-84EC1124B5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0798FDFF-83A0-440B-A4A2-84A5B5DEF6F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="46">
   <si>
     <t>Observaciones</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Grupo 14</t>
   </si>
   <si>
-    <t>https://github.com/rcfdtools/R.HCMC/blob/main/activity/M01A06/Readme.md</t>
-  </si>
-  <si>
     <t>M01A06</t>
   </si>
   <si>
@@ -252,12 +249,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -265,6 +256,12 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -283,7 +280,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -522,15 +519,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -540,7 +528,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -634,43 +622,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -707,6 +659,39 @@
     </xf>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2124,25 +2109,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="42" t="s">
-        <v>39</v>
+      <c r="F1" s="30" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
     </row>
     <row r="3" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="31"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
+      <c r="B3" s="43"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
     </row>
     <row r="4" spans="2:6" ht="27.75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="24" t="s">
@@ -2165,14 +2150,14 @@
       <c r="B5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="31">
         <v>5</v>
       </c>
       <c r="D5" s="25">
         <f>Detalle!C36*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="45"/>
+      <c r="E5" s="33"/>
       <c r="F5" s="15">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2182,14 +2167,14 @@
       <c r="B6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="31">
         <v>5</v>
       </c>
       <c r="D6" s="25">
         <f>Detalle!F36*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="45"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="15">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2199,14 +2184,14 @@
       <c r="B7" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="31">
         <v>5</v>
       </c>
       <c r="D7" s="25">
         <f>Detalle!I36*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="45"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2216,14 +2201,14 @@
       <c r="B8" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="31">
         <v>5</v>
       </c>
       <c r="D8" s="25">
         <f>Detalle!L36*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="45"/>
+      <c r="E8" s="33"/>
       <c r="F8" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2233,14 +2218,14 @@
       <c r="B9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="31">
         <v>5</v>
       </c>
       <c r="D9" s="25">
         <f>Detalle!O36*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="45"/>
+      <c r="E9" s="33"/>
       <c r="F9" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2250,14 +2235,14 @@
       <c r="B10" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="31">
         <v>5</v>
       </c>
       <c r="D10" s="25">
         <f>Detalle!O37*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="45"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2267,14 +2252,14 @@
       <c r="B11" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="43">
+      <c r="C11" s="31">
         <v>5</v>
       </c>
       <c r="D11" s="25">
         <f>Detalle!O38*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="45"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2284,14 +2269,14 @@
       <c r="B12" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="43">
+      <c r="C12" s="31">
         <v>5</v>
       </c>
       <c r="D12" s="25">
         <f>Detalle!O39*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="45"/>
+      <c r="E12" s="33"/>
       <c r="F12" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2301,14 +2286,14 @@
       <c r="B13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="43">
+      <c r="C13" s="31">
         <v>5</v>
       </c>
       <c r="D13" s="25">
         <f>Detalle!O40*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="45"/>
+      <c r="E13" s="33"/>
       <c r="F13" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2318,14 +2303,14 @@
       <c r="B14" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="43">
+      <c r="C14" s="31">
         <v>5</v>
       </c>
       <c r="D14" s="25">
         <f>Detalle!O41*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="45"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2335,14 +2320,14 @@
       <c r="B15" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="43">
+      <c r="C15" s="31">
         <v>5</v>
       </c>
       <c r="D15" s="25">
         <f>Detalle!O42*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="45"/>
+      <c r="E15" s="33"/>
       <c r="F15" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2352,14 +2337,14 @@
       <c r="B16" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="31">
         <v>5</v>
       </c>
       <c r="D16" s="25">
         <f>Detalle!AJ36*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="45"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2369,14 +2354,14 @@
       <c r="B17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="43">
+      <c r="C17" s="31">
         <v>5</v>
       </c>
       <c r="D17" s="25">
         <f>Detalle!AM36*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="45"/>
+      <c r="E17" s="33"/>
       <c r="F17" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2386,34 +2371,35 @@
       <c r="B18" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="32">
         <v>5</v>
       </c>
       <c r="D18" s="26">
         <f>Detalle!AP36*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="46"/>
+      <c r="E18" s="34"/>
       <c r="F18" s="17">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="41"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
+      <c r="B19" s="52" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A06 en GitHub.</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="40"/>
-      <c r="F20" s="40"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="28"/>
@@ -2423,17 +2409,15 @@
       <c r="F21" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
     <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="B19" r:id="rId1" xr:uid="{4745FAD9-0CA9-4A40-9B06-343197A406D4}"/>
-  </hyperlinks>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2513,96 +2497,96 @@
     </row>
     <row r="2" spans="1:44" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="7"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="32" t="str">
+      <c r="C2" s="49" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="33"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="32" t="str">
+      <c r="D2" s="50"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="49" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="32" t="str">
+      <c r="G2" s="50"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="49" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="32" t="str">
+      <c r="J2" s="50"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="49" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="33"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="32" t="str">
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="49" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="32" t="str">
+      <c r="P2" s="50"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="49" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="33"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="32" t="str">
+      <c r="S2" s="50"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="49" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="33"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="32" t="str">
+      <c r="V2" s="50"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="49" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="32" t="str">
+      <c r="Y2" s="50"/>
+      <c r="Z2" s="51"/>
+      <c r="AA2" s="49" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="33"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="32" t="str">
+      <c r="AB2" s="50"/>
+      <c r="AC2" s="51"/>
+      <c r="AD2" s="49" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="33"/>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="32" t="str">
+      <c r="AE2" s="50"/>
+      <c r="AF2" s="51"/>
+      <c r="AG2" s="49" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="33"/>
-      <c r="AI2" s="34"/>
-      <c r="AJ2" s="32" t="str">
+      <c r="AH2" s="50"/>
+      <c r="AI2" s="51"/>
+      <c r="AJ2" s="49" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="33"/>
-      <c r="AL2" s="34"/>
-      <c r="AM2" s="32" t="str">
+      <c r="AK2" s="50"/>
+      <c r="AL2" s="51"/>
+      <c r="AM2" s="49" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="33"/>
-      <c r="AO2" s="34"/>
-      <c r="AP2" s="32" t="str">
+      <c r="AN2" s="50"/>
+      <c r="AO2" s="51"/>
+      <c r="AP2" s="49" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="33"/>
-      <c r="AR2" s="34"/>
+      <c r="AQ2" s="50"/>
+      <c r="AR2" s="51"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="39"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
@@ -2734,1915 +2718,1915 @@
       <c r="B4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="47"/>
+      <c r="C4" s="35"/>
       <c r="D4" s="27"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="35"/>
       <c r="G4" s="27"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="47"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="35"/>
       <c r="J4" s="27"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="47"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="35"/>
       <c r="M4" s="27"/>
-      <c r="N4" s="48"/>
-      <c r="O4" s="47"/>
+      <c r="N4" s="36"/>
+      <c r="O4" s="35"/>
       <c r="P4" s="27"/>
-      <c r="Q4" s="48"/>
-      <c r="R4" s="47"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="35"/>
       <c r="S4" s="27"/>
-      <c r="T4" s="48"/>
-      <c r="U4" s="47"/>
+      <c r="T4" s="36"/>
+      <c r="U4" s="35"/>
       <c r="V4" s="27"/>
-      <c r="W4" s="48"/>
-      <c r="X4" s="47"/>
+      <c r="W4" s="36"/>
+      <c r="X4" s="35"/>
       <c r="Y4" s="27"/>
-      <c r="Z4" s="48"/>
-      <c r="AA4" s="47"/>
+      <c r="Z4" s="36"/>
+      <c r="AA4" s="35"/>
       <c r="AB4" s="27"/>
-      <c r="AC4" s="48"/>
-      <c r="AD4" s="47"/>
+      <c r="AC4" s="36"/>
+      <c r="AD4" s="35"/>
       <c r="AE4" s="27"/>
-      <c r="AF4" s="48"/>
-      <c r="AG4" s="47"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="35"/>
       <c r="AH4" s="27"/>
-      <c r="AI4" s="48"/>
-      <c r="AJ4" s="47"/>
+      <c r="AI4" s="36"/>
+      <c r="AJ4" s="35"/>
       <c r="AK4" s="27"/>
-      <c r="AL4" s="48"/>
-      <c r="AM4" s="47"/>
+      <c r="AL4" s="36"/>
+      <c r="AM4" s="35"/>
       <c r="AN4" s="27"/>
-      <c r="AO4" s="48"/>
-      <c r="AP4" s="47"/>
+      <c r="AO4" s="36"/>
+      <c r="AP4" s="35"/>
       <c r="AQ4" s="27"/>
-      <c r="AR4" s="48"/>
+      <c r="AR4" s="36"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B5" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="35">
         <v>0</v>
       </c>
       <c r="D5" s="27"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="47">
+      <c r="E5" s="36"/>
+      <c r="F5" s="35">
         <v>0</v>
       </c>
       <c r="G5" s="27"/>
-      <c r="H5" s="48"/>
-      <c r="I5" s="47">
+      <c r="H5" s="36"/>
+      <c r="I5" s="35">
         <v>0</v>
       </c>
       <c r="J5" s="27"/>
-      <c r="K5" s="48"/>
-      <c r="L5" s="47">
+      <c r="K5" s="36"/>
+      <c r="L5" s="35">
         <v>0</v>
       </c>
       <c r="M5" s="27"/>
-      <c r="N5" s="48"/>
-      <c r="O5" s="47">
+      <c r="N5" s="36"/>
+      <c r="O5" s="35">
         <v>0</v>
       </c>
       <c r="P5" s="27"/>
-      <c r="Q5" s="48"/>
-      <c r="R5" s="47">
+      <c r="Q5" s="36"/>
+      <c r="R5" s="35">
         <v>0</v>
       </c>
       <c r="S5" s="27"/>
-      <c r="T5" s="48"/>
-      <c r="U5" s="47">
+      <c r="T5" s="36"/>
+      <c r="U5" s="35">
         <v>0</v>
       </c>
       <c r="V5" s="27"/>
-      <c r="W5" s="48"/>
-      <c r="X5" s="47">
+      <c r="W5" s="36"/>
+      <c r="X5" s="35">
         <v>0</v>
       </c>
       <c r="Y5" s="27"/>
-      <c r="Z5" s="48"/>
-      <c r="AA5" s="47">
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="35">
         <v>0</v>
       </c>
       <c r="AB5" s="27"/>
-      <c r="AC5" s="48"/>
-      <c r="AD5" s="47">
+      <c r="AC5" s="36"/>
+      <c r="AD5" s="35">
         <v>0</v>
       </c>
       <c r="AE5" s="27"/>
-      <c r="AF5" s="48"/>
-      <c r="AG5" s="47">
+      <c r="AF5" s="36"/>
+      <c r="AG5" s="35">
         <v>0</v>
       </c>
       <c r="AH5" s="27"/>
-      <c r="AI5" s="48"/>
-      <c r="AJ5" s="47">
+      <c r="AI5" s="36"/>
+      <c r="AJ5" s="35">
         <v>0</v>
       </c>
       <c r="AK5" s="27"/>
-      <c r="AL5" s="48"/>
-      <c r="AM5" s="47">
+      <c r="AL5" s="36"/>
+      <c r="AM5" s="35">
         <v>0</v>
       </c>
       <c r="AN5" s="27"/>
-      <c r="AO5" s="48"/>
-      <c r="AP5" s="47">
+      <c r="AO5" s="36"/>
+      <c r="AP5" s="35">
         <v>0</v>
       </c>
       <c r="AQ5" s="27"/>
-      <c r="AR5" s="48"/>
+      <c r="AR5" s="36"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="47"/>
+      <c r="C6" s="35"/>
       <c r="D6" s="27"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="47"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="35"/>
       <c r="G6" s="27"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="47"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="35"/>
       <c r="J6" s="27"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="47"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="27"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="47"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="35"/>
       <c r="P6" s="27"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="47"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="35"/>
       <c r="S6" s="27"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="47"/>
+      <c r="T6" s="36"/>
+      <c r="U6" s="35"/>
       <c r="V6" s="27"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="47"/>
+      <c r="W6" s="36"/>
+      <c r="X6" s="35"/>
       <c r="Y6" s="27"/>
-      <c r="Z6" s="48"/>
-      <c r="AA6" s="47"/>
+      <c r="Z6" s="36"/>
+      <c r="AA6" s="35"/>
       <c r="AB6" s="27"/>
-      <c r="AC6" s="48"/>
-      <c r="AD6" s="47"/>
+      <c r="AC6" s="36"/>
+      <c r="AD6" s="35"/>
       <c r="AE6" s="27"/>
-      <c r="AF6" s="48"/>
-      <c r="AG6" s="47"/>
+      <c r="AF6" s="36"/>
+      <c r="AG6" s="35"/>
       <c r="AH6" s="27"/>
-      <c r="AI6" s="48"/>
-      <c r="AJ6" s="47"/>
+      <c r="AI6" s="36"/>
+      <c r="AJ6" s="35"/>
       <c r="AK6" s="27"/>
-      <c r="AL6" s="48"/>
-      <c r="AM6" s="47"/>
+      <c r="AL6" s="36"/>
+      <c r="AM6" s="35"/>
       <c r="AN6" s="27"/>
-      <c r="AO6" s="48"/>
-      <c r="AP6" s="47"/>
+      <c r="AO6" s="36"/>
+      <c r="AP6" s="35"/>
       <c r="AQ6" s="27"/>
-      <c r="AR6" s="48"/>
+      <c r="AR6" s="36"/>
     </row>
     <row r="7" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B7" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" s="47"/>
+        <v>40</v>
+      </c>
+      <c r="C7" s="35"/>
       <c r="D7" s="27"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="47"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="35"/>
       <c r="G7" s="27"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="47"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="35"/>
       <c r="J7" s="27"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="47"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="27"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="47"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="35"/>
       <c r="P7" s="27"/>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="47"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="35"/>
       <c r="S7" s="27"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="47"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="35"/>
       <c r="V7" s="27"/>
-      <c r="W7" s="48"/>
-      <c r="X7" s="47"/>
+      <c r="W7" s="36"/>
+      <c r="X7" s="35"/>
       <c r="Y7" s="27"/>
-      <c r="Z7" s="48"/>
-      <c r="AA7" s="47"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="35"/>
       <c r="AB7" s="27"/>
-      <c r="AC7" s="48"/>
-      <c r="AD7" s="47"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="35"/>
       <c r="AE7" s="27"/>
-      <c r="AF7" s="48"/>
-      <c r="AG7" s="47"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="35"/>
       <c r="AH7" s="27"/>
-      <c r="AI7" s="48"/>
-      <c r="AJ7" s="47"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="35"/>
       <c r="AK7" s="27"/>
-      <c r="AL7" s="48"/>
-      <c r="AM7" s="47"/>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="35"/>
       <c r="AN7" s="27"/>
-      <c r="AO7" s="48"/>
-      <c r="AP7" s="47"/>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="35"/>
       <c r="AQ7" s="27"/>
-      <c r="AR7" s="48"/>
+      <c r="AR7" s="36"/>
     </row>
     <row r="8" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" s="47"/>
+        <v>43</v>
+      </c>
+      <c r="C8" s="35"/>
       <c r="D8" s="29"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="47"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="35"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="48"/>
-      <c r="I8" s="47"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="35"/>
       <c r="J8" s="29"/>
-      <c r="K8" s="48"/>
-      <c r="L8" s="47"/>
+      <c r="K8" s="36"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="29"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="47"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="35"/>
       <c r="P8" s="29"/>
-      <c r="Q8" s="48"/>
-      <c r="R8" s="47"/>
+      <c r="Q8" s="36"/>
+      <c r="R8" s="35"/>
       <c r="S8" s="29"/>
-      <c r="T8" s="48"/>
-      <c r="U8" s="47"/>
+      <c r="T8" s="36"/>
+      <c r="U8" s="35"/>
       <c r="V8" s="29"/>
-      <c r="W8" s="48"/>
-      <c r="X8" s="47"/>
+      <c r="W8" s="36"/>
+      <c r="X8" s="35"/>
       <c r="Y8" s="29"/>
-      <c r="Z8" s="48"/>
-      <c r="AA8" s="47"/>
+      <c r="Z8" s="36"/>
+      <c r="AA8" s="35"/>
       <c r="AB8" s="29"/>
-      <c r="AC8" s="48"/>
-      <c r="AD8" s="47"/>
+      <c r="AC8" s="36"/>
+      <c r="AD8" s="35"/>
       <c r="AE8" s="29"/>
-      <c r="AF8" s="48"/>
-      <c r="AG8" s="47"/>
+      <c r="AF8" s="36"/>
+      <c r="AG8" s="35"/>
       <c r="AH8" s="29"/>
-      <c r="AI8" s="48"/>
-      <c r="AJ8" s="47"/>
+      <c r="AI8" s="36"/>
+      <c r="AJ8" s="35"/>
       <c r="AK8" s="29"/>
-      <c r="AL8" s="48"/>
-      <c r="AM8" s="47"/>
+      <c r="AL8" s="36"/>
+      <c r="AM8" s="35"/>
       <c r="AN8" s="29"/>
-      <c r="AO8" s="48"/>
-      <c r="AP8" s="47"/>
+      <c r="AO8" s="36"/>
+      <c r="AP8" s="35"/>
       <c r="AQ8" s="29"/>
-      <c r="AR8" s="48"/>
+      <c r="AR8" s="36"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="47"/>
+      <c r="C9" s="35"/>
       <c r="D9" s="27"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="47"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="35"/>
       <c r="G9" s="27"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="47"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="35"/>
       <c r="J9" s="27"/>
-      <c r="K9" s="48"/>
-      <c r="L9" s="47"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="27"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="47"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="35"/>
       <c r="P9" s="27"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="47"/>
+      <c r="Q9" s="36"/>
+      <c r="R9" s="35"/>
       <c r="S9" s="27"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="47"/>
+      <c r="T9" s="36"/>
+      <c r="U9" s="35"/>
       <c r="V9" s="27"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="47"/>
+      <c r="W9" s="36"/>
+      <c r="X9" s="35"/>
       <c r="Y9" s="27"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="47"/>
+      <c r="Z9" s="36"/>
+      <c r="AA9" s="35"/>
       <c r="AB9" s="27"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="47"/>
+      <c r="AC9" s="36"/>
+      <c r="AD9" s="35"/>
       <c r="AE9" s="27"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="47"/>
+      <c r="AF9" s="36"/>
+      <c r="AG9" s="35"/>
       <c r="AH9" s="27"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="47"/>
+      <c r="AI9" s="36"/>
+      <c r="AJ9" s="35"/>
       <c r="AK9" s="27"/>
-      <c r="AL9" s="48"/>
-      <c r="AM9" s="47"/>
+      <c r="AL9" s="36"/>
+      <c r="AM9" s="35"/>
       <c r="AN9" s="27"/>
-      <c r="AO9" s="48"/>
-      <c r="AP9" s="47"/>
+      <c r="AO9" s="36"/>
+      <c r="AP9" s="35"/>
       <c r="AQ9" s="27"/>
-      <c r="AR9" s="48"/>
+      <c r="AR9" s="36"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B10" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="51">
+      <c r="C10" s="35"/>
+      <c r="D10" s="39">
         <f>D9-D8</f>
         <v>0</v>
       </c>
-      <c r="E10" s="48"/>
-      <c r="F10" s="47"/>
-      <c r="G10" s="51">
+      <c r="E10" s="36"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="39">
         <f>G9-G8</f>
         <v>0</v>
       </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="51">
+      <c r="H10" s="36"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="39">
         <f>J9-J8</f>
         <v>0</v>
       </c>
-      <c r="K10" s="48"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="51">
+      <c r="K10" s="36"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="39">
         <f>M9-M8</f>
         <v>0</v>
       </c>
-      <c r="N10" s="48"/>
-      <c r="O10" s="47"/>
-      <c r="P10" s="51">
+      <c r="N10" s="36"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="39">
         <f>P9-P8</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="48"/>
-      <c r="R10" s="47"/>
-      <c r="S10" s="51">
+      <c r="Q10" s="36"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="39">
         <f>S9-S8</f>
         <v>0</v>
       </c>
-      <c r="T10" s="48"/>
-      <c r="U10" s="47"/>
-      <c r="V10" s="51">
+      <c r="T10" s="36"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="39">
         <f>V9-V8</f>
         <v>0</v>
       </c>
-      <c r="W10" s="48"/>
-      <c r="X10" s="47"/>
-      <c r="Y10" s="51">
+      <c r="W10" s="36"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="39">
         <f>Y9-Y8</f>
         <v>0</v>
       </c>
-      <c r="Z10" s="48"/>
-      <c r="AA10" s="47"/>
-      <c r="AB10" s="51">
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="39">
         <f>AB9-AB8</f>
         <v>0</v>
       </c>
-      <c r="AC10" s="48"/>
-      <c r="AD10" s="47"/>
-      <c r="AE10" s="51">
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="39">
         <f>AE9-AE8</f>
         <v>0</v>
       </c>
-      <c r="AF10" s="48"/>
-      <c r="AG10" s="47"/>
-      <c r="AH10" s="51">
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="39">
         <f>AH9-AH8</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="48"/>
-      <c r="AJ10" s="47"/>
-      <c r="AK10" s="51">
+      <c r="AI10" s="36"/>
+      <c r="AJ10" s="35"/>
+      <c r="AK10" s="39">
         <f>AK9-AK8</f>
         <v>0</v>
       </c>
-      <c r="AL10" s="48"/>
-      <c r="AM10" s="47"/>
-      <c r="AN10" s="51">
+      <c r="AL10" s="36"/>
+      <c r="AM10" s="35"/>
+      <c r="AN10" s="39">
         <f>AN9-AN8</f>
         <v>0</v>
       </c>
-      <c r="AO10" s="48"/>
-      <c r="AP10" s="47"/>
-      <c r="AQ10" s="51">
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="35"/>
+      <c r="AQ10" s="39">
         <f>AQ9-AQ8</f>
         <v>0</v>
       </c>
-      <c r="AR10" s="48"/>
+      <c r="AR10" s="36"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="47"/>
+      <c r="C11" s="35"/>
       <c r="D11" s="27"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="47"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="35"/>
       <c r="G11" s="27"/>
-      <c r="H11" s="48"/>
-      <c r="I11" s="47"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="35"/>
       <c r="J11" s="27"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="47"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="27"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="47"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="35"/>
       <c r="P11" s="27"/>
-      <c r="Q11" s="48"/>
-      <c r="R11" s="47"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="35"/>
       <c r="S11" s="27"/>
-      <c r="T11" s="48"/>
-      <c r="U11" s="47"/>
+      <c r="T11" s="36"/>
+      <c r="U11" s="35"/>
       <c r="V11" s="27"/>
-      <c r="W11" s="48"/>
-      <c r="X11" s="47"/>
+      <c r="W11" s="36"/>
+      <c r="X11" s="35"/>
       <c r="Y11" s="27"/>
-      <c r="Z11" s="48"/>
-      <c r="AA11" s="47"/>
+      <c r="Z11" s="36"/>
+      <c r="AA11" s="35"/>
       <c r="AB11" s="27"/>
-      <c r="AC11" s="48"/>
-      <c r="AD11" s="47"/>
+      <c r="AC11" s="36"/>
+      <c r="AD11" s="35"/>
       <c r="AE11" s="27"/>
-      <c r="AF11" s="48"/>
-      <c r="AG11" s="47"/>
+      <c r="AF11" s="36"/>
+      <c r="AG11" s="35"/>
       <c r="AH11" s="27"/>
-      <c r="AI11" s="48"/>
-      <c r="AJ11" s="47"/>
+      <c r="AI11" s="36"/>
+      <c r="AJ11" s="35"/>
       <c r="AK11" s="27"/>
-      <c r="AL11" s="48"/>
-      <c r="AM11" s="47"/>
+      <c r="AL11" s="36"/>
+      <c r="AM11" s="35"/>
       <c r="AN11" s="27"/>
-      <c r="AO11" s="48"/>
-      <c r="AP11" s="47"/>
+      <c r="AO11" s="36"/>
+      <c r="AP11" s="35"/>
       <c r="AQ11" s="27"/>
-      <c r="AR11" s="48"/>
+      <c r="AR11" s="36"/>
     </row>
     <row r="12" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B12" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="47"/>
+        <v>41</v>
+      </c>
+      <c r="C12" s="35"/>
       <c r="D12" s="27"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="47"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="35"/>
       <c r="G12" s="27"/>
-      <c r="H12" s="48"/>
-      <c r="I12" s="47"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="35"/>
       <c r="J12" s="27"/>
-      <c r="K12" s="48"/>
-      <c r="L12" s="47"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="27"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="47"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="35"/>
       <c r="P12" s="27"/>
-      <c r="Q12" s="48"/>
-      <c r="R12" s="47"/>
+      <c r="Q12" s="36"/>
+      <c r="R12" s="35"/>
       <c r="S12" s="27"/>
-      <c r="T12" s="48"/>
-      <c r="U12" s="47"/>
+      <c r="T12" s="36"/>
+      <c r="U12" s="35"/>
       <c r="V12" s="27"/>
-      <c r="W12" s="48"/>
-      <c r="X12" s="47"/>
+      <c r="W12" s="36"/>
+      <c r="X12" s="35"/>
       <c r="Y12" s="27"/>
-      <c r="Z12" s="48"/>
-      <c r="AA12" s="47"/>
+      <c r="Z12" s="36"/>
+      <c r="AA12" s="35"/>
       <c r="AB12" s="27"/>
-      <c r="AC12" s="48"/>
-      <c r="AD12" s="47"/>
+      <c r="AC12" s="36"/>
+      <c r="AD12" s="35"/>
       <c r="AE12" s="27"/>
-      <c r="AF12" s="48"/>
-      <c r="AG12" s="47"/>
+      <c r="AF12" s="36"/>
+      <c r="AG12" s="35"/>
       <c r="AH12" s="27"/>
-      <c r="AI12" s="48"/>
-      <c r="AJ12" s="47"/>
+      <c r="AI12" s="36"/>
+      <c r="AJ12" s="35"/>
       <c r="AK12" s="27"/>
-      <c r="AL12" s="48"/>
-      <c r="AM12" s="47"/>
+      <c r="AL12" s="36"/>
+      <c r="AM12" s="35"/>
       <c r="AN12" s="27"/>
-      <c r="AO12" s="48"/>
-      <c r="AP12" s="47"/>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="35"/>
       <c r="AQ12" s="27"/>
-      <c r="AR12" s="48"/>
+      <c r="AR12" s="36"/>
     </row>
     <row r="13" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B13" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="47"/>
+        <v>42</v>
+      </c>
+      <c r="C13" s="35"/>
       <c r="D13" s="27"/>
-      <c r="E13" s="48"/>
-      <c r="F13" s="47"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="35"/>
       <c r="G13" s="27"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="47"/>
+      <c r="H13" s="36"/>
+      <c r="I13" s="35"/>
       <c r="J13" s="27"/>
-      <c r="K13" s="48"/>
-      <c r="L13" s="47"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="35"/>
       <c r="M13" s="27"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="47"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="35"/>
       <c r="P13" s="27"/>
-      <c r="Q13" s="48"/>
-      <c r="R13" s="47"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="35"/>
       <c r="S13" s="27"/>
-      <c r="T13" s="48"/>
-      <c r="U13" s="47"/>
+      <c r="T13" s="36"/>
+      <c r="U13" s="35"/>
       <c r="V13" s="27"/>
-      <c r="W13" s="48"/>
-      <c r="X13" s="47"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="35"/>
       <c r="Y13" s="27"/>
-      <c r="Z13" s="48"/>
-      <c r="AA13" s="47"/>
+      <c r="Z13" s="36"/>
+      <c r="AA13" s="35"/>
       <c r="AB13" s="27"/>
-      <c r="AC13" s="48"/>
-      <c r="AD13" s="47"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="35"/>
       <c r="AE13" s="27"/>
-      <c r="AF13" s="48"/>
-      <c r="AG13" s="47"/>
+      <c r="AF13" s="36"/>
+      <c r="AG13" s="35"/>
       <c r="AH13" s="27"/>
-      <c r="AI13" s="48"/>
-      <c r="AJ13" s="47"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="35"/>
       <c r="AK13" s="27"/>
-      <c r="AL13" s="48"/>
-      <c r="AM13" s="47"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="35"/>
       <c r="AN13" s="27"/>
-      <c r="AO13" s="48"/>
-      <c r="AP13" s="47"/>
+      <c r="AO13" s="36"/>
+      <c r="AP13" s="35"/>
       <c r="AQ13" s="27"/>
-      <c r="AR13" s="48"/>
+      <c r="AR13" s="36"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="47"/>
-      <c r="D14" s="50">
+      <c r="C14" s="35"/>
+      <c r="D14" s="38">
         <f>D11-D8</f>
         <v>0</v>
       </c>
-      <c r="E14" s="48"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="50">
+      <c r="E14" s="36"/>
+      <c r="F14" s="35"/>
+      <c r="G14" s="38">
         <f>G11-G8</f>
         <v>0</v>
       </c>
-      <c r="H14" s="48"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="50">
+      <c r="H14" s="36"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="38">
         <f>J11-J8</f>
         <v>0</v>
       </c>
-      <c r="K14" s="48"/>
-      <c r="L14" s="47"/>
-      <c r="M14" s="50">
+      <c r="K14" s="36"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="38">
         <f>M11-M8</f>
         <v>0</v>
       </c>
-      <c r="N14" s="48"/>
-      <c r="O14" s="47"/>
-      <c r="P14" s="50">
+      <c r="N14" s="36"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="38">
         <f>P11-P8</f>
         <v>0</v>
       </c>
-      <c r="Q14" s="48"/>
-      <c r="R14" s="47"/>
-      <c r="S14" s="50">
+      <c r="Q14" s="36"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="38">
         <f>S11-S8</f>
         <v>0</v>
       </c>
-      <c r="T14" s="48"/>
-      <c r="U14" s="47"/>
-      <c r="V14" s="50">
+      <c r="T14" s="36"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="38">
         <f>V11-V8</f>
         <v>0</v>
       </c>
-      <c r="W14" s="48"/>
-      <c r="X14" s="47"/>
-      <c r="Y14" s="50">
+      <c r="W14" s="36"/>
+      <c r="X14" s="35"/>
+      <c r="Y14" s="38">
         <f>Y11-Y8</f>
         <v>0</v>
       </c>
-      <c r="Z14" s="48"/>
-      <c r="AA14" s="47"/>
-      <c r="AB14" s="50">
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="35"/>
+      <c r="AB14" s="38">
         <f>AB11-AB8</f>
         <v>0</v>
       </c>
-      <c r="AC14" s="48"/>
-      <c r="AD14" s="47"/>
-      <c r="AE14" s="50">
+      <c r="AC14" s="36"/>
+      <c r="AD14" s="35"/>
+      <c r="AE14" s="38">
         <f>AE11-AE8</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="48"/>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="50">
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="35"/>
+      <c r="AH14" s="38">
         <f>AH11-AH8</f>
         <v>0</v>
       </c>
-      <c r="AI14" s="48"/>
-      <c r="AJ14" s="47"/>
-      <c r="AK14" s="50">
+      <c r="AI14" s="36"/>
+      <c r="AJ14" s="35"/>
+      <c r="AK14" s="38">
         <f>AK11-AK8</f>
         <v>0</v>
       </c>
-      <c r="AL14" s="48"/>
-      <c r="AM14" s="47"/>
-      <c r="AN14" s="50">
+      <c r="AL14" s="36"/>
+      <c r="AM14" s="35"/>
+      <c r="AN14" s="38">
         <f>AN11-AN8</f>
         <v>0</v>
       </c>
-      <c r="AO14" s="48"/>
-      <c r="AP14" s="47"/>
-      <c r="AQ14" s="50">
+      <c r="AO14" s="36"/>
+      <c r="AP14" s="35"/>
+      <c r="AQ14" s="38">
         <f>AQ11-AQ8</f>
         <v>0</v>
       </c>
-      <c r="AR14" s="48"/>
+      <c r="AR14" s="36"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="47"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="49"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="49"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="47"/>
-      <c r="P15" s="49"/>
-      <c r="Q15" s="48"/>
-      <c r="R15" s="47"/>
-      <c r="S15" s="49"/>
-      <c r="T15" s="48"/>
-      <c r="U15" s="47"/>
-      <c r="V15" s="49"/>
-      <c r="W15" s="48"/>
-      <c r="X15" s="47"/>
-      <c r="Y15" s="49"/>
-      <c r="Z15" s="48"/>
-      <c r="AA15" s="47"/>
-      <c r="AB15" s="49"/>
-      <c r="AC15" s="48"/>
-      <c r="AD15" s="47"/>
-      <c r="AE15" s="49"/>
-      <c r="AF15" s="48"/>
-      <c r="AG15" s="47"/>
-      <c r="AH15" s="49"/>
-      <c r="AI15" s="48"/>
-      <c r="AJ15" s="47"/>
-      <c r="AK15" s="49"/>
-      <c r="AL15" s="48"/>
-      <c r="AM15" s="47"/>
-      <c r="AN15" s="49"/>
-      <c r="AO15" s="48"/>
-      <c r="AP15" s="47"/>
-      <c r="AQ15" s="49"/>
-      <c r="AR15" s="48"/>
+      <c r="C15" s="35"/>
+      <c r="D15" s="37"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="35"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="36"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="37"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="36"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="37"/>
+      <c r="T15" s="36"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="37"/>
+      <c r="W15" s="36"/>
+      <c r="X15" s="35"/>
+      <c r="Y15" s="37"/>
+      <c r="Z15" s="36"/>
+      <c r="AA15" s="35"/>
+      <c r="AB15" s="37"/>
+      <c r="AC15" s="36"/>
+      <c r="AD15" s="35"/>
+      <c r="AE15" s="37"/>
+      <c r="AF15" s="36"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="37"/>
+      <c r="AI15" s="36"/>
+      <c r="AJ15" s="35"/>
+      <c r="AK15" s="37"/>
+      <c r="AL15" s="36"/>
+      <c r="AM15" s="35"/>
+      <c r="AN15" s="37"/>
+      <c r="AO15" s="36"/>
+      <c r="AP15" s="35"/>
+      <c r="AQ15" s="37"/>
+      <c r="AR15" s="36"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B16" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="47"/>
+      <c r="C16" s="35"/>
       <c r="D16" s="27"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="47"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="35"/>
       <c r="G16" s="27"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="47"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="35"/>
       <c r="J16" s="27"/>
-      <c r="K16" s="48"/>
-      <c r="L16" s="47"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="35"/>
       <c r="M16" s="27"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="47"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="35"/>
       <c r="P16" s="27"/>
-      <c r="Q16" s="48"/>
-      <c r="R16" s="47"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="35"/>
       <c r="S16" s="27"/>
-      <c r="T16" s="48"/>
-      <c r="U16" s="47"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="35"/>
       <c r="V16" s="27"/>
-      <c r="W16" s="48"/>
-      <c r="X16" s="47"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="35"/>
       <c r="Y16" s="27"/>
-      <c r="Z16" s="48"/>
-      <c r="AA16" s="47"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="35"/>
       <c r="AB16" s="27"/>
-      <c r="AC16" s="48"/>
-      <c r="AD16" s="47"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="35"/>
       <c r="AE16" s="27"/>
-      <c r="AF16" s="48"/>
-      <c r="AG16" s="47"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="35"/>
       <c r="AH16" s="27"/>
-      <c r="AI16" s="48"/>
-      <c r="AJ16" s="47"/>
+      <c r="AI16" s="36"/>
+      <c r="AJ16" s="35"/>
       <c r="AK16" s="27"/>
-      <c r="AL16" s="48"/>
-      <c r="AM16" s="47"/>
+      <c r="AL16" s="36"/>
+      <c r="AM16" s="35"/>
       <c r="AN16" s="27"/>
-      <c r="AO16" s="48"/>
-      <c r="AP16" s="47"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="35"/>
       <c r="AQ16" s="27"/>
-      <c r="AR16" s="48"/>
+      <c r="AR16" s="36"/>
     </row>
     <row r="17" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="47"/>
+      <c r="C17" s="35"/>
       <c r="D17" s="27"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="47"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="35"/>
       <c r="G17" s="27"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="47"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="35"/>
       <c r="J17" s="27"/>
-      <c r="K17" s="48"/>
-      <c r="L17" s="47"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="35"/>
       <c r="M17" s="27"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="47"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="35"/>
       <c r="P17" s="27"/>
-      <c r="Q17" s="48"/>
-      <c r="R17" s="47"/>
+      <c r="Q17" s="36"/>
+      <c r="R17" s="35"/>
       <c r="S17" s="27"/>
-      <c r="T17" s="48"/>
-      <c r="U17" s="47"/>
+      <c r="T17" s="36"/>
+      <c r="U17" s="35"/>
       <c r="V17" s="27"/>
-      <c r="W17" s="48"/>
-      <c r="X17" s="47"/>
+      <c r="W17" s="36"/>
+      <c r="X17" s="35"/>
       <c r="Y17" s="27"/>
-      <c r="Z17" s="48"/>
-      <c r="AA17" s="47"/>
+      <c r="Z17" s="36"/>
+      <c r="AA17" s="35"/>
       <c r="AB17" s="27"/>
-      <c r="AC17" s="48"/>
-      <c r="AD17" s="47"/>
+      <c r="AC17" s="36"/>
+      <c r="AD17" s="35"/>
       <c r="AE17" s="27"/>
-      <c r="AF17" s="48"/>
-      <c r="AG17" s="47"/>
+      <c r="AF17" s="36"/>
+      <c r="AG17" s="35"/>
       <c r="AH17" s="27"/>
-      <c r="AI17" s="48"/>
-      <c r="AJ17" s="47"/>
+      <c r="AI17" s="36"/>
+      <c r="AJ17" s="35"/>
       <c r="AK17" s="27"/>
-      <c r="AL17" s="48"/>
-      <c r="AM17" s="47"/>
+      <c r="AL17" s="36"/>
+      <c r="AM17" s="35"/>
       <c r="AN17" s="27"/>
-      <c r="AO17" s="48"/>
-      <c r="AP17" s="47"/>
+      <c r="AO17" s="36"/>
+      <c r="AP17" s="35"/>
       <c r="AQ17" s="27"/>
-      <c r="AR17" s="48"/>
+      <c r="AR17" s="36"/>
     </row>
     <row r="18" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B18" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="47"/>
+      <c r="C18" s="35"/>
       <c r="D18" s="27"/>
-      <c r="E18" s="48"/>
-      <c r="F18" s="47"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="35"/>
       <c r="G18" s="27"/>
-      <c r="H18" s="48"/>
-      <c r="I18" s="47"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="35"/>
       <c r="J18" s="27"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="47"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="35"/>
       <c r="M18" s="27"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="47"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="35"/>
       <c r="P18" s="27"/>
-      <c r="Q18" s="48"/>
-      <c r="R18" s="47"/>
+      <c r="Q18" s="36"/>
+      <c r="R18" s="35"/>
       <c r="S18" s="27"/>
-      <c r="T18" s="48"/>
-      <c r="U18" s="47"/>
+      <c r="T18" s="36"/>
+      <c r="U18" s="35"/>
       <c r="V18" s="27"/>
-      <c r="W18" s="48"/>
-      <c r="X18" s="47"/>
+      <c r="W18" s="36"/>
+      <c r="X18" s="35"/>
       <c r="Y18" s="27"/>
-      <c r="Z18" s="48"/>
-      <c r="AA18" s="47"/>
+      <c r="Z18" s="36"/>
+      <c r="AA18" s="35"/>
       <c r="AB18" s="27"/>
-      <c r="AC18" s="48"/>
-      <c r="AD18" s="47"/>
+      <c r="AC18" s="36"/>
+      <c r="AD18" s="35"/>
       <c r="AE18" s="27"/>
-      <c r="AF18" s="48"/>
-      <c r="AG18" s="47"/>
+      <c r="AF18" s="36"/>
+      <c r="AG18" s="35"/>
       <c r="AH18" s="27"/>
-      <c r="AI18" s="48"/>
-      <c r="AJ18" s="47"/>
+      <c r="AI18" s="36"/>
+      <c r="AJ18" s="35"/>
       <c r="AK18" s="27"/>
-      <c r="AL18" s="48"/>
-      <c r="AM18" s="47"/>
+      <c r="AL18" s="36"/>
+      <c r="AM18" s="35"/>
       <c r="AN18" s="27"/>
-      <c r="AO18" s="48"/>
-      <c r="AP18" s="47"/>
+      <c r="AO18" s="36"/>
+      <c r="AP18" s="35"/>
       <c r="AQ18" s="27"/>
-      <c r="AR18" s="48"/>
+      <c r="AR18" s="36"/>
     </row>
     <row r="19" spans="2:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B19" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="47"/>
+        <v>40</v>
+      </c>
+      <c r="C19" s="35"/>
       <c r="D19" s="27"/>
-      <c r="E19" s="48"/>
-      <c r="F19" s="47"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="35"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="48"/>
-      <c r="I19" s="47"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="35"/>
       <c r="J19" s="27"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="47"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="35"/>
       <c r="M19" s="27"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="47"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="35"/>
       <c r="P19" s="27"/>
-      <c r="Q19" s="48"/>
-      <c r="R19" s="47"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="35"/>
       <c r="S19" s="27"/>
-      <c r="T19" s="48"/>
-      <c r="U19" s="47"/>
+      <c r="T19" s="36"/>
+      <c r="U19" s="35"/>
       <c r="V19" s="27"/>
-      <c r="W19" s="48"/>
-      <c r="X19" s="47"/>
+      <c r="W19" s="36"/>
+      <c r="X19" s="35"/>
       <c r="Y19" s="27"/>
-      <c r="Z19" s="48"/>
-      <c r="AA19" s="47"/>
+      <c r="Z19" s="36"/>
+      <c r="AA19" s="35"/>
       <c r="AB19" s="27"/>
-      <c r="AC19" s="48"/>
-      <c r="AD19" s="47"/>
+      <c r="AC19" s="36"/>
+      <c r="AD19" s="35"/>
       <c r="AE19" s="27"/>
-      <c r="AF19" s="48"/>
-      <c r="AG19" s="47"/>
+      <c r="AF19" s="36"/>
+      <c r="AG19" s="35"/>
       <c r="AH19" s="27"/>
-      <c r="AI19" s="48"/>
-      <c r="AJ19" s="47"/>
+      <c r="AI19" s="36"/>
+      <c r="AJ19" s="35"/>
       <c r="AK19" s="27"/>
-      <c r="AL19" s="48"/>
-      <c r="AM19" s="47"/>
+      <c r="AL19" s="36"/>
+      <c r="AM19" s="35"/>
       <c r="AN19" s="27"/>
-      <c r="AO19" s="48"/>
-      <c r="AP19" s="47"/>
+      <c r="AO19" s="36"/>
+      <c r="AP19" s="35"/>
       <c r="AQ19" s="27"/>
-      <c r="AR19" s="48"/>
+      <c r="AR19" s="36"/>
     </row>
     <row r="20" spans="2:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="47"/>
+        <v>43</v>
+      </c>
+      <c r="C20" s="35"/>
       <c r="D20" s="29"/>
-      <c r="E20" s="48"/>
-      <c r="F20" s="47"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="35"/>
       <c r="G20" s="29"/>
-      <c r="H20" s="48"/>
-      <c r="I20" s="47"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="35"/>
       <c r="J20" s="29"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="47"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="35"/>
       <c r="M20" s="29"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="47"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="35"/>
       <c r="P20" s="29"/>
-      <c r="Q20" s="48"/>
-      <c r="R20" s="47"/>
+      <c r="Q20" s="36"/>
+      <c r="R20" s="35"/>
       <c r="S20" s="29"/>
-      <c r="T20" s="48"/>
-      <c r="U20" s="47"/>
+      <c r="T20" s="36"/>
+      <c r="U20" s="35"/>
       <c r="V20" s="29"/>
-      <c r="W20" s="48"/>
-      <c r="X20" s="47"/>
+      <c r="W20" s="36"/>
+      <c r="X20" s="35"/>
       <c r="Y20" s="29"/>
-      <c r="Z20" s="48"/>
-      <c r="AA20" s="47"/>
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="35"/>
       <c r="AB20" s="29"/>
-      <c r="AC20" s="48"/>
-      <c r="AD20" s="47"/>
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="35"/>
       <c r="AE20" s="29"/>
-      <c r="AF20" s="48"/>
-      <c r="AG20" s="47"/>
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="35"/>
       <c r="AH20" s="29"/>
-      <c r="AI20" s="48"/>
-      <c r="AJ20" s="47"/>
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="35"/>
       <c r="AK20" s="29"/>
-      <c r="AL20" s="48"/>
-      <c r="AM20" s="47"/>
+      <c r="AL20" s="36"/>
+      <c r="AM20" s="35"/>
       <c r="AN20" s="29"/>
-      <c r="AO20" s="48"/>
-      <c r="AP20" s="47"/>
+      <c r="AO20" s="36"/>
+      <c r="AP20" s="35"/>
       <c r="AQ20" s="29"/>
-      <c r="AR20" s="48"/>
+      <c r="AR20" s="36"/>
     </row>
     <row r="21" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="47"/>
+      <c r="C21" s="35"/>
       <c r="D21" s="27"/>
-      <c r="E21" s="48"/>
-      <c r="F21" s="47"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="35"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="48"/>
-      <c r="I21" s="47"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="35"/>
       <c r="J21" s="27"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="47"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="35"/>
       <c r="M21" s="27"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="47"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="35"/>
       <c r="P21" s="27"/>
-      <c r="Q21" s="48"/>
-      <c r="R21" s="47"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="35"/>
       <c r="S21" s="27"/>
-      <c r="T21" s="48"/>
-      <c r="U21" s="47"/>
+      <c r="T21" s="36"/>
+      <c r="U21" s="35"/>
       <c r="V21" s="27"/>
-      <c r="W21" s="48"/>
-      <c r="X21" s="47"/>
+      <c r="W21" s="36"/>
+      <c r="X21" s="35"/>
       <c r="Y21" s="27"/>
-      <c r="Z21" s="48"/>
-      <c r="AA21" s="47"/>
+      <c r="Z21" s="36"/>
+      <c r="AA21" s="35"/>
       <c r="AB21" s="27"/>
-      <c r="AC21" s="48"/>
-      <c r="AD21" s="47"/>
+      <c r="AC21" s="36"/>
+      <c r="AD21" s="35"/>
       <c r="AE21" s="27"/>
-      <c r="AF21" s="48"/>
-      <c r="AG21" s="47"/>
+      <c r="AF21" s="36"/>
+      <c r="AG21" s="35"/>
       <c r="AH21" s="27"/>
-      <c r="AI21" s="48"/>
-      <c r="AJ21" s="47"/>
+      <c r="AI21" s="36"/>
+      <c r="AJ21" s="35"/>
       <c r="AK21" s="27"/>
-      <c r="AL21" s="48"/>
-      <c r="AM21" s="47"/>
+      <c r="AL21" s="36"/>
+      <c r="AM21" s="35"/>
       <c r="AN21" s="27"/>
-      <c r="AO21" s="48"/>
-      <c r="AP21" s="47"/>
+      <c r="AO21" s="36"/>
+      <c r="AP21" s="35"/>
       <c r="AQ21" s="27"/>
-      <c r="AR21" s="48"/>
+      <c r="AR21" s="36"/>
     </row>
     <row r="22" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="47"/>
-      <c r="D22" s="51">
+      <c r="C22" s="35"/>
+      <c r="D22" s="39">
         <f>D21-D20</f>
         <v>0</v>
       </c>
-      <c r="E22" s="48"/>
-      <c r="F22" s="47"/>
-      <c r="G22" s="51">
+      <c r="E22" s="36"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="39">
         <f>G21-G20</f>
         <v>0</v>
       </c>
-      <c r="H22" s="48"/>
-      <c r="I22" s="47"/>
-      <c r="J22" s="51">
+      <c r="H22" s="36"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="39">
         <f>J21-J20</f>
         <v>0</v>
       </c>
-      <c r="K22" s="48"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="51">
+      <c r="K22" s="36"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="39">
         <f>M21-M20</f>
         <v>0</v>
       </c>
-      <c r="N22" s="48"/>
-      <c r="O22" s="47"/>
-      <c r="P22" s="51">
+      <c r="N22" s="36"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="39">
         <f>P21-P20</f>
         <v>0</v>
       </c>
-      <c r="Q22" s="48"/>
-      <c r="R22" s="47"/>
-      <c r="S22" s="51">
+      <c r="Q22" s="36"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="39">
         <f>S21-S20</f>
         <v>0</v>
       </c>
-      <c r="T22" s="48"/>
-      <c r="U22" s="47"/>
-      <c r="V22" s="51">
+      <c r="T22" s="36"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="39">
         <f>V21-V20</f>
         <v>0</v>
       </c>
-      <c r="W22" s="48"/>
-      <c r="X22" s="47"/>
-      <c r="Y22" s="51">
+      <c r="W22" s="36"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="39">
         <f>Y21-Y20</f>
         <v>0</v>
       </c>
-      <c r="Z22" s="48"/>
-      <c r="AA22" s="47"/>
-      <c r="AB22" s="51">
+      <c r="Z22" s="36"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="39">
         <f>AB21-AB20</f>
         <v>0</v>
       </c>
-      <c r="AC22" s="48"/>
-      <c r="AD22" s="47"/>
-      <c r="AE22" s="51">
+      <c r="AC22" s="36"/>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="39">
         <f>AE21-AE20</f>
         <v>0</v>
       </c>
-      <c r="AF22" s="48"/>
-      <c r="AG22" s="47"/>
-      <c r="AH22" s="51">
+      <c r="AF22" s="36"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22" s="39">
         <f>AH21-AH20</f>
         <v>0</v>
       </c>
-      <c r="AI22" s="48"/>
-      <c r="AJ22" s="47"/>
-      <c r="AK22" s="51">
+      <c r="AI22" s="36"/>
+      <c r="AJ22" s="35"/>
+      <c r="AK22" s="39">
         <f>AK21-AK20</f>
         <v>0</v>
       </c>
-      <c r="AL22" s="48"/>
-      <c r="AM22" s="47"/>
-      <c r="AN22" s="51">
+      <c r="AL22" s="36"/>
+      <c r="AM22" s="35"/>
+      <c r="AN22" s="39">
         <f>AN21-AN20</f>
         <v>0</v>
       </c>
-      <c r="AO22" s="48"/>
-      <c r="AP22" s="47"/>
-      <c r="AQ22" s="51">
+      <c r="AO22" s="36"/>
+      <c r="AP22" s="35"/>
+      <c r="AQ22" s="39">
         <f>AQ21-AQ20</f>
         <v>0</v>
       </c>
-      <c r="AR22" s="48"/>
+      <c r="AR22" s="36"/>
     </row>
     <row r="23" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B23" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="47"/>
+      <c r="C23" s="35"/>
       <c r="D23" s="27"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="47"/>
+      <c r="E23" s="36"/>
+      <c r="F23" s="35"/>
       <c r="G23" s="27"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="47"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="35"/>
       <c r="J23" s="27"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="47"/>
+      <c r="K23" s="36"/>
+      <c r="L23" s="35"/>
       <c r="M23" s="27"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="47"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="35"/>
       <c r="P23" s="27"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="47"/>
+      <c r="Q23" s="36"/>
+      <c r="R23" s="35"/>
       <c r="S23" s="27"/>
-      <c r="T23" s="48"/>
-      <c r="U23" s="47"/>
+      <c r="T23" s="36"/>
+      <c r="U23" s="35"/>
       <c r="V23" s="27"/>
-      <c r="W23" s="48"/>
-      <c r="X23" s="47"/>
+      <c r="W23" s="36"/>
+      <c r="X23" s="35"/>
       <c r="Y23" s="27"/>
-      <c r="Z23" s="48"/>
-      <c r="AA23" s="47"/>
+      <c r="Z23" s="36"/>
+      <c r="AA23" s="35"/>
       <c r="AB23" s="27"/>
-      <c r="AC23" s="48"/>
-      <c r="AD23" s="47"/>
+      <c r="AC23" s="36"/>
+      <c r="AD23" s="35"/>
       <c r="AE23" s="27"/>
-      <c r="AF23" s="48"/>
-      <c r="AG23" s="47"/>
+      <c r="AF23" s="36"/>
+      <c r="AG23" s="35"/>
       <c r="AH23" s="27"/>
-      <c r="AI23" s="48"/>
-      <c r="AJ23" s="47"/>
+      <c r="AI23" s="36"/>
+      <c r="AJ23" s="35"/>
       <c r="AK23" s="27"/>
-      <c r="AL23" s="48"/>
-      <c r="AM23" s="47"/>
+      <c r="AL23" s="36"/>
+      <c r="AM23" s="35"/>
       <c r="AN23" s="27"/>
-      <c r="AO23" s="48"/>
-      <c r="AP23" s="47"/>
+      <c r="AO23" s="36"/>
+      <c r="AP23" s="35"/>
       <c r="AQ23" s="27"/>
-      <c r="AR23" s="48"/>
+      <c r="AR23" s="36"/>
     </row>
     <row r="24" spans="2:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="47"/>
+        <v>41</v>
+      </c>
+      <c r="C24" s="35"/>
       <c r="D24" s="27"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="47"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="35"/>
       <c r="G24" s="27"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="47"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="35"/>
       <c r="J24" s="27"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="47"/>
+      <c r="K24" s="36"/>
+      <c r="L24" s="35"/>
       <c r="M24" s="27"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="47"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="35"/>
       <c r="P24" s="27"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="47"/>
+      <c r="Q24" s="36"/>
+      <c r="R24" s="35"/>
       <c r="S24" s="27"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="47"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="35"/>
       <c r="V24" s="27"/>
-      <c r="W24" s="48"/>
-      <c r="X24" s="47"/>
+      <c r="W24" s="36"/>
+      <c r="X24" s="35"/>
       <c r="Y24" s="27"/>
-      <c r="Z24" s="48"/>
-      <c r="AA24" s="47"/>
+      <c r="Z24" s="36"/>
+      <c r="AA24" s="35"/>
       <c r="AB24" s="27"/>
-      <c r="AC24" s="48"/>
-      <c r="AD24" s="47"/>
+      <c r="AC24" s="36"/>
+      <c r="AD24" s="35"/>
       <c r="AE24" s="27"/>
-      <c r="AF24" s="48"/>
-      <c r="AG24" s="47"/>
+      <c r="AF24" s="36"/>
+      <c r="AG24" s="35"/>
       <c r="AH24" s="27"/>
-      <c r="AI24" s="48"/>
-      <c r="AJ24" s="47"/>
+      <c r="AI24" s="36"/>
+      <c r="AJ24" s="35"/>
       <c r="AK24" s="27"/>
-      <c r="AL24" s="48"/>
-      <c r="AM24" s="47"/>
+      <c r="AL24" s="36"/>
+      <c r="AM24" s="35"/>
       <c r="AN24" s="27"/>
-      <c r="AO24" s="48"/>
-      <c r="AP24" s="47"/>
+      <c r="AO24" s="36"/>
+      <c r="AP24" s="35"/>
       <c r="AQ24" s="27"/>
-      <c r="AR24" s="48"/>
+      <c r="AR24" s="36"/>
     </row>
     <row r="25" spans="2:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B25" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="47"/>
+        <v>42</v>
+      </c>
+      <c r="C25" s="35"/>
       <c r="D25" s="27"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="47"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="35"/>
       <c r="G25" s="27"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="47"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="35"/>
       <c r="J25" s="27"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="47"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="35"/>
       <c r="M25" s="27"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="47"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="35"/>
       <c r="P25" s="27"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="47"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="35"/>
       <c r="S25" s="27"/>
-      <c r="T25" s="48"/>
-      <c r="U25" s="47"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="35"/>
       <c r="V25" s="27"/>
-      <c r="W25" s="48"/>
-      <c r="X25" s="47"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="35"/>
       <c r="Y25" s="27"/>
-      <c r="Z25" s="48"/>
-      <c r="AA25" s="47"/>
+      <c r="Z25" s="36"/>
+      <c r="AA25" s="35"/>
       <c r="AB25" s="27"/>
-      <c r="AC25" s="48"/>
-      <c r="AD25" s="47"/>
+      <c r="AC25" s="36"/>
+      <c r="AD25" s="35"/>
       <c r="AE25" s="27"/>
-      <c r="AF25" s="48"/>
-      <c r="AG25" s="47"/>
+      <c r="AF25" s="36"/>
+      <c r="AG25" s="35"/>
       <c r="AH25" s="27"/>
-      <c r="AI25" s="48"/>
-      <c r="AJ25" s="47"/>
+      <c r="AI25" s="36"/>
+      <c r="AJ25" s="35"/>
       <c r="AK25" s="27"/>
-      <c r="AL25" s="48"/>
-      <c r="AM25" s="47"/>
+      <c r="AL25" s="36"/>
+      <c r="AM25" s="35"/>
       <c r="AN25" s="27"/>
-      <c r="AO25" s="48"/>
-      <c r="AP25" s="47"/>
+      <c r="AO25" s="36"/>
+      <c r="AP25" s="35"/>
       <c r="AQ25" s="27"/>
-      <c r="AR25" s="48"/>
+      <c r="AR25" s="36"/>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B26" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C26" s="47"/>
-      <c r="D26" s="50">
+      <c r="C26" s="35"/>
+      <c r="D26" s="38">
         <f>D23-D20</f>
         <v>0</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="47"/>
-      <c r="G26" s="50">
+      <c r="E26" s="36"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="38">
         <f>G23-G20</f>
         <v>0</v>
       </c>
-      <c r="H26" s="48"/>
-      <c r="I26" s="47"/>
-      <c r="J26" s="50">
+      <c r="H26" s="36"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="38">
         <f>J23-J20</f>
         <v>0</v>
       </c>
-      <c r="K26" s="48"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="50">
+      <c r="K26" s="36"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="38">
         <f>M23-M20</f>
         <v>0</v>
       </c>
-      <c r="N26" s="48"/>
-      <c r="O26" s="47"/>
-      <c r="P26" s="50">
+      <c r="N26" s="36"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="38">
         <f>P23-P20</f>
         <v>0</v>
       </c>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="47"/>
-      <c r="S26" s="50">
+      <c r="Q26" s="36"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="38">
         <f>S23-S20</f>
         <v>0</v>
       </c>
-      <c r="T26" s="48"/>
-      <c r="U26" s="47"/>
-      <c r="V26" s="50">
+      <c r="T26" s="36"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="38">
         <f>V23-V20</f>
         <v>0</v>
       </c>
-      <c r="W26" s="48"/>
-      <c r="X26" s="47"/>
-      <c r="Y26" s="50">
+      <c r="W26" s="36"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="38">
         <f>Y23-Y20</f>
         <v>0</v>
       </c>
-      <c r="Z26" s="48"/>
-      <c r="AA26" s="47"/>
-      <c r="AB26" s="50">
+      <c r="Z26" s="36"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="38">
         <f>AB23-AB20</f>
         <v>0</v>
       </c>
-      <c r="AC26" s="48"/>
-      <c r="AD26" s="47"/>
-      <c r="AE26" s="50">
+      <c r="AC26" s="36"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="38">
         <f>AE23-AE20</f>
         <v>0</v>
       </c>
-      <c r="AF26" s="48"/>
-      <c r="AG26" s="47"/>
-      <c r="AH26" s="50">
+      <c r="AF26" s="36"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="38">
         <f>AH23-AH20</f>
         <v>0</v>
       </c>
-      <c r="AI26" s="48"/>
-      <c r="AJ26" s="47"/>
-      <c r="AK26" s="50">
+      <c r="AI26" s="36"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="38">
         <f>AK23-AK20</f>
         <v>0</v>
       </c>
-      <c r="AL26" s="48"/>
-      <c r="AM26" s="47"/>
-      <c r="AN26" s="50">
+      <c r="AL26" s="36"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="38">
         <f>AN23-AN20</f>
         <v>0</v>
       </c>
-      <c r="AO26" s="48"/>
-      <c r="AP26" s="47"/>
-      <c r="AQ26" s="50">
+      <c r="AO26" s="36"/>
+      <c r="AP26" s="35"/>
+      <c r="AQ26" s="38">
         <f>AQ23-AQ20</f>
         <v>0</v>
       </c>
-      <c r="AR26" s="48"/>
+      <c r="AR26" s="36"/>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B27" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C27" s="47"/>
-      <c r="D27" s="49"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="49"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="49"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="47"/>
-      <c r="P27" s="49"/>
-      <c r="Q27" s="48"/>
-      <c r="R27" s="47"/>
-      <c r="S27" s="49"/>
-      <c r="T27" s="48"/>
-      <c r="U27" s="47"/>
-      <c r="V27" s="49"/>
-      <c r="W27" s="48"/>
-      <c r="X27" s="47"/>
-      <c r="Y27" s="49"/>
-      <c r="Z27" s="48"/>
-      <c r="AA27" s="47"/>
-      <c r="AB27" s="49"/>
-      <c r="AC27" s="48"/>
-      <c r="AD27" s="47"/>
-      <c r="AE27" s="49"/>
-      <c r="AF27" s="48"/>
-      <c r="AG27" s="47"/>
-      <c r="AH27" s="49"/>
-      <c r="AI27" s="48"/>
-      <c r="AJ27" s="47"/>
-      <c r="AK27" s="49"/>
-      <c r="AL27" s="48"/>
-      <c r="AM27" s="47"/>
-      <c r="AN27" s="49"/>
-      <c r="AO27" s="48"/>
-      <c r="AP27" s="47"/>
-      <c r="AQ27" s="49"/>
-      <c r="AR27" s="48"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="36"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="37"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="35"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="37"/>
+      <c r="W27" s="36"/>
+      <c r="X27" s="35"/>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="36"/>
+      <c r="AA27" s="35"/>
+      <c r="AB27" s="37"/>
+      <c r="AC27" s="36"/>
+      <c r="AD27" s="35"/>
+      <c r="AE27" s="37"/>
+      <c r="AF27" s="36"/>
+      <c r="AG27" s="35"/>
+      <c r="AH27" s="37"/>
+      <c r="AI27" s="36"/>
+      <c r="AJ27" s="35"/>
+      <c r="AK27" s="37"/>
+      <c r="AL27" s="36"/>
+      <c r="AM27" s="35"/>
+      <c r="AN27" s="37"/>
+      <c r="AO27" s="36"/>
+      <c r="AP27" s="35"/>
+      <c r="AQ27" s="37"/>
+      <c r="AR27" s="36"/>
     </row>
     <row r="28" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B28" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="C28" s="47"/>
+      <c r="C28" s="35"/>
       <c r="D28" s="27"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="47"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="35"/>
       <c r="G28" s="27"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="47"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="35"/>
       <c r="J28" s="27"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="47"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="35"/>
       <c r="M28" s="27"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="47"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="35"/>
       <c r="P28" s="27"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="47"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="35"/>
       <c r="S28" s="27"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="47"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="35"/>
       <c r="V28" s="27"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="47"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="35"/>
       <c r="Y28" s="27"/>
-      <c r="Z28" s="48"/>
-      <c r="AA28" s="47"/>
+      <c r="Z28" s="36"/>
+      <c r="AA28" s="35"/>
       <c r="AB28" s="27"/>
-      <c r="AC28" s="48"/>
-      <c r="AD28" s="47"/>
+      <c r="AC28" s="36"/>
+      <c r="AD28" s="35"/>
       <c r="AE28" s="27"/>
-      <c r="AF28" s="48"/>
-      <c r="AG28" s="47"/>
+      <c r="AF28" s="36"/>
+      <c r="AG28" s="35"/>
       <c r="AH28" s="27"/>
-      <c r="AI28" s="48"/>
-      <c r="AJ28" s="47"/>
+      <c r="AI28" s="36"/>
+      <c r="AJ28" s="35"/>
       <c r="AK28" s="27"/>
-      <c r="AL28" s="48"/>
-      <c r="AM28" s="47"/>
+      <c r="AL28" s="36"/>
+      <c r="AM28" s="35"/>
       <c r="AN28" s="27"/>
-      <c r="AO28" s="48"/>
-      <c r="AP28" s="47"/>
+      <c r="AO28" s="36"/>
+      <c r="AP28" s="35"/>
       <c r="AQ28" s="27"/>
-      <c r="AR28" s="48"/>
+      <c r="AR28" s="36"/>
     </row>
     <row r="29" spans="2:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B29" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="47"/>
-      <c r="D29" s="52">
+        <v>39</v>
+      </c>
+      <c r="C29" s="35"/>
+      <c r="D29" s="40">
         <f>D6-D18</f>
         <v>0</v>
       </c>
-      <c r="E29" s="48"/>
-      <c r="F29" s="47"/>
-      <c r="G29" s="52">
+      <c r="E29" s="36"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="40">
         <f>G6-G18</f>
         <v>0</v>
       </c>
-      <c r="H29" s="48"/>
-      <c r="I29" s="47"/>
-      <c r="J29" s="52">
+      <c r="H29" s="36"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="40">
         <f>J6-J18</f>
         <v>0</v>
       </c>
-      <c r="K29" s="48"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="52">
+      <c r="K29" s="36"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="40">
         <f>M6-M18</f>
         <v>0</v>
       </c>
-      <c r="N29" s="48"/>
-      <c r="O29" s="47"/>
-      <c r="P29" s="52">
+      <c r="N29" s="36"/>
+      <c r="O29" s="35"/>
+      <c r="P29" s="40">
         <f>P6-P18</f>
         <v>0</v>
       </c>
-      <c r="Q29" s="48"/>
-      <c r="R29" s="47"/>
-      <c r="S29" s="52">
+      <c r="Q29" s="36"/>
+      <c r="R29" s="35"/>
+      <c r="S29" s="40">
         <f>S6-S18</f>
         <v>0</v>
       </c>
-      <c r="T29" s="48"/>
-      <c r="U29" s="47"/>
-      <c r="V29" s="52">
+      <c r="T29" s="36"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="40">
         <f>V6-V18</f>
         <v>0</v>
       </c>
-      <c r="W29" s="48"/>
-      <c r="X29" s="47"/>
-      <c r="Y29" s="52">
+      <c r="W29" s="36"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="40">
         <f>Y6-Y18</f>
         <v>0</v>
       </c>
-      <c r="Z29" s="48"/>
-      <c r="AA29" s="47"/>
-      <c r="AB29" s="52">
+      <c r="Z29" s="36"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="40">
         <f>AB6-AB18</f>
         <v>0</v>
       </c>
-      <c r="AC29" s="48"/>
-      <c r="AD29" s="47"/>
-      <c r="AE29" s="52">
+      <c r="AC29" s="36"/>
+      <c r="AD29" s="35"/>
+      <c r="AE29" s="40">
         <f>AE6-AE18</f>
         <v>0</v>
       </c>
-      <c r="AF29" s="48"/>
-      <c r="AG29" s="47"/>
-      <c r="AH29" s="52">
+      <c r="AF29" s="36"/>
+      <c r="AG29" s="35"/>
+      <c r="AH29" s="40">
         <f>AH6-AH18</f>
         <v>0</v>
       </c>
-      <c r="AI29" s="48"/>
-      <c r="AJ29" s="47"/>
-      <c r="AK29" s="52">
+      <c r="AI29" s="36"/>
+      <c r="AJ29" s="35"/>
+      <c r="AK29" s="40">
         <f>AK6-AK18</f>
         <v>0</v>
       </c>
-      <c r="AL29" s="48"/>
-      <c r="AM29" s="47"/>
-      <c r="AN29" s="52">
+      <c r="AL29" s="36"/>
+      <c r="AM29" s="35"/>
+      <c r="AN29" s="40">
         <f>AN6-AN18</f>
         <v>0</v>
       </c>
-      <c r="AO29" s="48"/>
-      <c r="AP29" s="47"/>
-      <c r="AQ29" s="52">
+      <c r="AO29" s="36"/>
+      <c r="AP29" s="35"/>
+      <c r="AQ29" s="40">
         <f>AQ6-AQ18</f>
         <v>0</v>
       </c>
-      <c r="AR29" s="48"/>
+      <c r="AR29" s="36"/>
     </row>
     <row r="30" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B30" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="47"/>
-      <c r="D30" s="50">
+      <c r="C30" s="35"/>
+      <c r="D30" s="38">
         <f>D8-D20</f>
         <v>0</v>
       </c>
-      <c r="E30" s="48"/>
-      <c r="F30" s="47"/>
-      <c r="G30" s="50">
+      <c r="E30" s="36"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="38">
         <f>G8-G20</f>
         <v>0</v>
       </c>
-      <c r="H30" s="48"/>
-      <c r="I30" s="47"/>
-      <c r="J30" s="50">
+      <c r="H30" s="36"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="38">
         <f>J8-J20</f>
         <v>0</v>
       </c>
-      <c r="K30" s="48"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="50">
+      <c r="K30" s="36"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="38">
         <f>M8-M20</f>
         <v>0</v>
       </c>
-      <c r="N30" s="48"/>
-      <c r="O30" s="47"/>
-      <c r="P30" s="50">
+      <c r="N30" s="36"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="38">
         <f>P8-P20</f>
         <v>0</v>
       </c>
-      <c r="Q30" s="48"/>
-      <c r="R30" s="47"/>
-      <c r="S30" s="50">
+      <c r="Q30" s="36"/>
+      <c r="R30" s="35"/>
+      <c r="S30" s="38">
         <f>S8-S20</f>
         <v>0</v>
       </c>
-      <c r="T30" s="48"/>
-      <c r="U30" s="47"/>
-      <c r="V30" s="50">
+      <c r="T30" s="36"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="38">
         <f>V8-V20</f>
         <v>0</v>
       </c>
-      <c r="W30" s="48"/>
-      <c r="X30" s="47"/>
-      <c r="Y30" s="50">
+      <c r="W30" s="36"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="38">
         <f>Y8-Y20</f>
         <v>0</v>
       </c>
-      <c r="Z30" s="48"/>
-      <c r="AA30" s="47"/>
-      <c r="AB30" s="50">
+      <c r="Z30" s="36"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="38">
         <f>AB8-AB20</f>
         <v>0</v>
       </c>
-      <c r="AC30" s="48"/>
-      <c r="AD30" s="47"/>
-      <c r="AE30" s="50">
+      <c r="AC30" s="36"/>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="38">
         <f>AE8-AE20</f>
         <v>0</v>
       </c>
-      <c r="AF30" s="48"/>
-      <c r="AG30" s="47"/>
-      <c r="AH30" s="50">
+      <c r="AF30" s="36"/>
+      <c r="AG30" s="35"/>
+      <c r="AH30" s="38">
         <f>AH8-AH20</f>
         <v>0</v>
       </c>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="47"/>
-      <c r="AK30" s="50">
+      <c r="AI30" s="36"/>
+      <c r="AJ30" s="35"/>
+      <c r="AK30" s="38">
         <f>AK8-AK20</f>
         <v>0</v>
       </c>
-      <c r="AL30" s="48"/>
-      <c r="AM30" s="47"/>
-      <c r="AN30" s="50">
+      <c r="AL30" s="36"/>
+      <c r="AM30" s="35"/>
+      <c r="AN30" s="38">
         <f>AN8-AN20</f>
         <v>0</v>
       </c>
-      <c r="AO30" s="48"/>
-      <c r="AP30" s="47"/>
-      <c r="AQ30" s="50">
+      <c r="AO30" s="36"/>
+      <c r="AP30" s="35"/>
+      <c r="AQ30" s="38">
         <f>AQ8-AQ20</f>
         <v>0</v>
       </c>
-      <c r="AR30" s="48"/>
+      <c r="AR30" s="36"/>
     </row>
     <row r="31" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B31" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="53" t="e">
+      <c r="C31" s="35"/>
+      <c r="D31" s="41" t="e">
         <f>D30/D29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E31" s="48"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="53" t="e">
+      <c r="E31" s="36"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="41" t="e">
         <f>G30/G29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H31" s="48"/>
-      <c r="I31" s="47"/>
-      <c r="J31" s="53" t="e">
+      <c r="H31" s="36"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="41" t="e">
         <f>J30/J29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K31" s="48"/>
-      <c r="L31" s="47"/>
-      <c r="M31" s="53" t="e">
+      <c r="K31" s="36"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="41" t="e">
         <f>M30/M29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N31" s="48"/>
-      <c r="O31" s="47"/>
-      <c r="P31" s="53" t="e">
+      <c r="N31" s="36"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="41" t="e">
         <f>P30/P29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="47"/>
-      <c r="S31" s="53" t="e">
+      <c r="Q31" s="36"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="41" t="e">
         <f>S30/S29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T31" s="48"/>
-      <c r="U31" s="47"/>
-      <c r="V31" s="53" t="e">
+      <c r="T31" s="36"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="41" t="e">
         <f>V30/V29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W31" s="48"/>
-      <c r="X31" s="47"/>
-      <c r="Y31" s="53" t="e">
+      <c r="W31" s="36"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="41" t="e">
         <f>Y30/Y29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z31" s="48"/>
-      <c r="AA31" s="47"/>
-      <c r="AB31" s="53" t="e">
+      <c r="Z31" s="36"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="41" t="e">
         <f>AB30/AB29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC31" s="48"/>
-      <c r="AD31" s="47"/>
-      <c r="AE31" s="53" t="e">
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="41" t="e">
         <f>AE30/AE29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF31" s="48"/>
-      <c r="AG31" s="47"/>
-      <c r="AH31" s="53" t="e">
+      <c r="AF31" s="36"/>
+      <c r="AG31" s="35"/>
+      <c r="AH31" s="41" t="e">
         <f>AH30/AH29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="47"/>
-      <c r="AK31" s="53" t="e">
+      <c r="AI31" s="36"/>
+      <c r="AJ31" s="35"/>
+      <c r="AK31" s="41" t="e">
         <f>AK30/AK29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL31" s="48"/>
-      <c r="AM31" s="47"/>
-      <c r="AN31" s="53" t="e">
+      <c r="AL31" s="36"/>
+      <c r="AM31" s="35"/>
+      <c r="AN31" s="41" t="e">
         <f>AN30/AN29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO31" s="48"/>
-      <c r="AP31" s="47"/>
-      <c r="AQ31" s="53" t="e">
+      <c r="AO31" s="36"/>
+      <c r="AP31" s="35"/>
+      <c r="AQ31" s="41" t="e">
         <f>AQ30/AQ29</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR31" s="48"/>
+      <c r="AR31" s="36"/>
     </row>
     <row r="32" spans="2:44" ht="49.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="47"/>
+        <v>44</v>
+      </c>
+      <c r="C32" s="35"/>
       <c r="D32" s="27"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="47"/>
+      <c r="E32" s="36"/>
+      <c r="F32" s="35"/>
       <c r="G32" s="27"/>
-      <c r="H32" s="48"/>
-      <c r="I32" s="47"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="35"/>
       <c r="J32" s="27"/>
-      <c r="K32" s="48"/>
-      <c r="L32" s="47"/>
+      <c r="K32" s="36"/>
+      <c r="L32" s="35"/>
       <c r="M32" s="27"/>
-      <c r="N32" s="48"/>
-      <c r="O32" s="47"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="35"/>
       <c r="P32" s="27"/>
-      <c r="Q32" s="48"/>
-      <c r="R32" s="47"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="35"/>
       <c r="S32" s="27"/>
-      <c r="T32" s="48"/>
-      <c r="U32" s="47"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="35"/>
       <c r="V32" s="27"/>
-      <c r="W32" s="48"/>
-      <c r="X32" s="47"/>
+      <c r="W32" s="36"/>
+      <c r="X32" s="35"/>
       <c r="Y32" s="27"/>
-      <c r="Z32" s="48"/>
-      <c r="AA32" s="47"/>
+      <c r="Z32" s="36"/>
+      <c r="AA32" s="35"/>
       <c r="AB32" s="27"/>
-      <c r="AC32" s="48"/>
-      <c r="AD32" s="47"/>
+      <c r="AC32" s="36"/>
+      <c r="AD32" s="35"/>
       <c r="AE32" s="27"/>
-      <c r="AF32" s="48"/>
-      <c r="AG32" s="47"/>
+      <c r="AF32" s="36"/>
+      <c r="AG32" s="35"/>
       <c r="AH32" s="27"/>
-      <c r="AI32" s="48"/>
-      <c r="AJ32" s="47"/>
+      <c r="AI32" s="36"/>
+      <c r="AJ32" s="35"/>
       <c r="AK32" s="27"/>
-      <c r="AL32" s="48"/>
-      <c r="AM32" s="47"/>
+      <c r="AL32" s="36"/>
+      <c r="AM32" s="35"/>
       <c r="AN32" s="27"/>
-      <c r="AO32" s="48"/>
-      <c r="AP32" s="47"/>
+      <c r="AO32" s="36"/>
+      <c r="AP32" s="35"/>
       <c r="AQ32" s="27"/>
-      <c r="AR32" s="48"/>
+      <c r="AR32" s="36"/>
     </row>
     <row r="33" spans="1:44" ht="63.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B33" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="47"/>
+      <c r="C33" s="35"/>
       <c r="D33" s="27"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="47"/>
+      <c r="E33" s="36"/>
+      <c r="F33" s="35"/>
       <c r="G33" s="27"/>
-      <c r="H33" s="48"/>
-      <c r="I33" s="47"/>
+      <c r="H33" s="36"/>
+      <c r="I33" s="35"/>
       <c r="J33" s="27"/>
-      <c r="K33" s="48"/>
-      <c r="L33" s="47"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="27"/>
-      <c r="N33" s="48"/>
-      <c r="O33" s="47"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="35"/>
       <c r="P33" s="27"/>
-      <c r="Q33" s="48"/>
-      <c r="R33" s="47"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="35"/>
       <c r="S33" s="27"/>
-      <c r="T33" s="48"/>
-      <c r="U33" s="47"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="35"/>
       <c r="V33" s="27"/>
-      <c r="W33" s="48"/>
-      <c r="X33" s="47"/>
+      <c r="W33" s="36"/>
+      <c r="X33" s="35"/>
       <c r="Y33" s="27"/>
-      <c r="Z33" s="48"/>
-      <c r="AA33" s="47"/>
+      <c r="Z33" s="36"/>
+      <c r="AA33" s="35"/>
       <c r="AB33" s="27"/>
-      <c r="AC33" s="48"/>
-      <c r="AD33" s="47"/>
+      <c r="AC33" s="36"/>
+      <c r="AD33" s="35"/>
       <c r="AE33" s="27"/>
-      <c r="AF33" s="48"/>
-      <c r="AG33" s="47"/>
+      <c r="AF33" s="36"/>
+      <c r="AG33" s="35"/>
       <c r="AH33" s="27"/>
-      <c r="AI33" s="48"/>
-      <c r="AJ33" s="47"/>
+      <c r="AI33" s="36"/>
+      <c r="AJ33" s="35"/>
       <c r="AK33" s="27"/>
-      <c r="AL33" s="48"/>
-      <c r="AM33" s="47"/>
+      <c r="AL33" s="36"/>
+      <c r="AM33" s="35"/>
       <c r="AN33" s="27"/>
-      <c r="AO33" s="48"/>
-      <c r="AP33" s="47"/>
+      <c r="AO33" s="36"/>
+      <c r="AP33" s="35"/>
       <c r="AQ33" s="27"/>
-      <c r="AR33" s="48"/>
+      <c r="AR33" s="36"/>
     </row>
     <row r="34" spans="1:44" ht="93.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B34" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="47"/>
+        <v>45</v>
+      </c>
+      <c r="C34" s="35"/>
       <c r="D34" s="27"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="47"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="35"/>
       <c r="G34" s="27"/>
-      <c r="H34" s="48"/>
-      <c r="I34" s="47"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="35"/>
       <c r="J34" s="27"/>
-      <c r="K34" s="48"/>
-      <c r="L34" s="47"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="35"/>
       <c r="M34" s="27"/>
-      <c r="N34" s="48"/>
-      <c r="O34" s="47"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="35"/>
       <c r="P34" s="27"/>
-      <c r="Q34" s="48"/>
-      <c r="R34" s="47"/>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="35"/>
       <c r="S34" s="27"/>
-      <c r="T34" s="48"/>
-      <c r="U34" s="47"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="35"/>
       <c r="V34" s="27"/>
-      <c r="W34" s="48"/>
-      <c r="X34" s="47"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="35"/>
       <c r="Y34" s="27"/>
-      <c r="Z34" s="48"/>
-      <c r="AA34" s="47"/>
+      <c r="Z34" s="36"/>
+      <c r="AA34" s="35"/>
       <c r="AB34" s="27"/>
-      <c r="AC34" s="48"/>
-      <c r="AD34" s="47"/>
+      <c r="AC34" s="36"/>
+      <c r="AD34" s="35"/>
       <c r="AE34" s="27"/>
-      <c r="AF34" s="48"/>
-      <c r="AG34" s="47"/>
+      <c r="AF34" s="36"/>
+      <c r="AG34" s="35"/>
       <c r="AH34" s="27"/>
-      <c r="AI34" s="48"/>
-      <c r="AJ34" s="47"/>
+      <c r="AI34" s="36"/>
+      <c r="AJ34" s="35"/>
       <c r="AK34" s="27"/>
-      <c r="AL34" s="48"/>
-      <c r="AM34" s="47"/>
+      <c r="AL34" s="36"/>
+      <c r="AM34" s="35"/>
       <c r="AN34" s="27"/>
-      <c r="AO34" s="48"/>
-      <c r="AP34" s="47"/>
+      <c r="AO34" s="36"/>
+      <c r="AP34" s="35"/>
       <c r="AQ34" s="27"/>
-      <c r="AR34" s="48"/>
+      <c r="AR34" s="36"/>
     </row>
     <row r="35" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B35" s="12"/>
-      <c r="C35" s="47"/>
+      <c r="C35" s="35"/>
       <c r="D35" s="27"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="47"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="35"/>
       <c r="G35" s="27"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="47"/>
+      <c r="H35" s="36"/>
+      <c r="I35" s="35"/>
       <c r="J35" s="27"/>
-      <c r="K35" s="48"/>
-      <c r="L35" s="47"/>
+      <c r="K35" s="36"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="27"/>
-      <c r="N35" s="48"/>
-      <c r="O35" s="47"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="35"/>
       <c r="P35" s="27"/>
-      <c r="Q35" s="48"/>
-      <c r="R35" s="47"/>
+      <c r="Q35" s="36"/>
+      <c r="R35" s="35"/>
       <c r="S35" s="27"/>
-      <c r="T35" s="48"/>
-      <c r="U35" s="47"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="35"/>
       <c r="V35" s="27"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="47"/>
+      <c r="W35" s="36"/>
+      <c r="X35" s="35"/>
       <c r="Y35" s="27"/>
-      <c r="Z35" s="48"/>
-      <c r="AA35" s="47"/>
+      <c r="Z35" s="36"/>
+      <c r="AA35" s="35"/>
       <c r="AB35" s="27"/>
-      <c r="AC35" s="48"/>
-      <c r="AD35" s="47"/>
+      <c r="AC35" s="36"/>
+      <c r="AD35" s="35"/>
       <c r="AE35" s="27"/>
-      <c r="AF35" s="48"/>
-      <c r="AG35" s="47"/>
+      <c r="AF35" s="36"/>
+      <c r="AG35" s="35"/>
       <c r="AH35" s="27"/>
-      <c r="AI35" s="48"/>
-      <c r="AJ35" s="47"/>
+      <c r="AI35" s="36"/>
+      <c r="AJ35" s="35"/>
       <c r="AK35" s="27"/>
-      <c r="AL35" s="48"/>
-      <c r="AM35" s="47"/>
+      <c r="AL35" s="36"/>
+      <c r="AM35" s="35"/>
       <c r="AN35" s="27"/>
-      <c r="AO35" s="48"/>
-      <c r="AP35" s="47"/>
+      <c r="AO35" s="36"/>
+      <c r="AP35" s="35"/>
       <c r="AQ35" s="27"/>
-      <c r="AR35" s="48"/>
+      <c r="AR35" s="36"/>
     </row>
     <row r="36" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A36" s="1"/>
       <c r="B36" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="46">
         <f>AVERAGE(C4:C35)</f>
         <v>0</v>
       </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="35">
+      <c r="D36" s="47"/>
+      <c r="E36" s="48"/>
+      <c r="F36" s="46">
         <f>AVERAGE(F4:F35)</f>
         <v>0</v>
       </c>
-      <c r="G36" s="36"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="35">
+      <c r="G36" s="47"/>
+      <c r="H36" s="48"/>
+      <c r="I36" s="46">
         <f>AVERAGE(I4:I35)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="36"/>
-      <c r="K36" s="37"/>
-      <c r="L36" s="35">
+      <c r="J36" s="47"/>
+      <c r="K36" s="48"/>
+      <c r="L36" s="46">
         <f>AVERAGE(L4:L35)</f>
         <v>0</v>
       </c>
-      <c r="M36" s="36"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="35">
+      <c r="M36" s="47"/>
+      <c r="N36" s="48"/>
+      <c r="O36" s="46">
         <f>AVERAGE(O4:O35)</f>
         <v>0</v>
       </c>
-      <c r="P36" s="36"/>
-      <c r="Q36" s="37"/>
-      <c r="R36" s="35">
+      <c r="P36" s="47"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="46">
         <f>AVERAGE(R4:R35)</f>
         <v>0</v>
       </c>
-      <c r="S36" s="36"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="35">
+      <c r="S36" s="47"/>
+      <c r="T36" s="48"/>
+      <c r="U36" s="46">
         <f>AVERAGE(U4:U35)</f>
         <v>0</v>
       </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="37"/>
-      <c r="X36" s="35">
+      <c r="V36" s="47"/>
+      <c r="W36" s="48"/>
+      <c r="X36" s="46">
         <f>AVERAGE(X4:X35)</f>
         <v>0</v>
       </c>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="37"/>
-      <c r="AA36" s="35">
+      <c r="Y36" s="47"/>
+      <c r="Z36" s="48"/>
+      <c r="AA36" s="46">
         <f>AVERAGE(AA4:AA35)</f>
         <v>0</v>
       </c>
-      <c r="AB36" s="36"/>
-      <c r="AC36" s="37"/>
-      <c r="AD36" s="35">
+      <c r="AB36" s="47"/>
+      <c r="AC36" s="48"/>
+      <c r="AD36" s="46">
         <f>AVERAGE(AD4:AD35)</f>
         <v>0</v>
       </c>
-      <c r="AE36" s="36"/>
-      <c r="AF36" s="37"/>
-      <c r="AG36" s="35">
+      <c r="AE36" s="47"/>
+      <c r="AF36" s="48"/>
+      <c r="AG36" s="46">
         <f>AVERAGE(AG4:AG35)</f>
         <v>0</v>
       </c>
-      <c r="AH36" s="36"/>
-      <c r="AI36" s="37"/>
-      <c r="AJ36" s="35">
+      <c r="AH36" s="47"/>
+      <c r="AI36" s="48"/>
+      <c r="AJ36" s="46">
         <f>AVERAGE(AJ4:AJ35)</f>
         <v>0</v>
       </c>
-      <c r="AK36" s="36"/>
-      <c r="AL36" s="37"/>
-      <c r="AM36" s="35">
+      <c r="AK36" s="47"/>
+      <c r="AL36" s="48"/>
+      <c r="AM36" s="46">
         <f>AVERAGE(AM4:AM35)</f>
         <v>0</v>
       </c>
-      <c r="AN36" s="36"/>
-      <c r="AO36" s="37"/>
-      <c r="AP36" s="35">
+      <c r="AN36" s="47"/>
+      <c r="AO36" s="48"/>
+      <c r="AP36" s="46">
         <f>AVERAGE(AP4:AP35)</f>
         <v>0</v>
       </c>
-      <c r="AQ36" s="36"/>
-      <c r="AR36" s="37"/>
+      <c r="AQ36" s="47"/>
+      <c r="AR36" s="48"/>
     </row>
     <row r="37" spans="1:44" s="7" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B37" s="20"/>
@@ -6266,19 +6250,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="U36:W36"/>
-    <mergeCell ref="AM36:AO36"/>
-    <mergeCell ref="X36:Z36"/>
-    <mergeCell ref="AA36:AC36"/>
-    <mergeCell ref="AD36:AF36"/>
-    <mergeCell ref="AG36:AI36"/>
-    <mergeCell ref="AJ36:AL36"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I36:K36"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="R36:T36"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="C2:E2"/>
@@ -6295,6 +6266,19 @@
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="L2:N2"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="AM36:AO36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AG36:AI36"/>
+    <mergeCell ref="AJ36:AL36"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
